--- a/samples/2_devices_valid.xlsx
+++ b/samples/2_devices_valid.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,6 +436,8 @@
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,6 +519,16 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>management_ip6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>primary address v4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>primary address v6</t>
         </is>
       </c>
     </row>
@@ -573,6 +585,8 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -627,6 +641,8 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -701,6 +717,16 @@
           <t>2001:db8:1::11/64</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>192.0.2.11/24</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2001:db8:1::11/64</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -767,6 +793,12 @@
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>192.0.2.102/32</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -829,6 +861,12 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>192.0.2.103/32</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -883,6 +921,8 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -941,6 +981,12 @@
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>192.0.2.22/24</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1003,6 +1049,68 @@
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>192.0.2.21/24</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LAB1-DH1-R02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>lab1-dh1-r02-leaf02</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spectrum-SN4700</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Nvidia</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ns-leaf</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
